--- a/data/records/第5批次建议参数.xlsx
+++ b/data/records/第5批次建议参数.xlsx
@@ -480,16 +480,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B2" t="n">
-        <v>840</v>
+        <v>1040</v>
       </c>
       <c r="C2" t="n">
         <v>460</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
@@ -498,13 +498,13 @@
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,28 +520,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B3" t="n">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="C3" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="n">
         <v>30</v>
-      </c>
-      <c r="G3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H3" t="n">
-        <v>25</v>
       </c>
       <c r="I3" t="n">
         <v>30</v>
@@ -560,19 +560,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" t="n">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="C4" t="n">
         <v>460</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
@@ -581,10 +581,10 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,16 +600,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B5" t="n">
-        <v>860</v>
+        <v>960</v>
       </c>
       <c r="C5" t="n">
         <v>460</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
@@ -621,10 +621,10 @@
         <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>

--- a/data/records/第5批次建议参数.xlsx
+++ b/data/records/第5批次建议参数.xlsx
@@ -483,28 +483,28 @@
         <v>141</v>
       </c>
       <c r="B2" t="n">
-        <v>1040</v>
+        <v>920</v>
       </c>
       <c r="C2" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,28 +520,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" t="n">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="C3" t="n">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
         <v>30</v>
@@ -560,19 +560,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" t="n">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="C4" t="n">
         <v>460</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
@@ -581,10 +581,10 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,31 +600,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B5" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="C5" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>

--- a/data/records/第5批次建议参数.xlsx
+++ b/data/records/第5批次建议参数.xlsx
@@ -483,19 +483,19 @@
         <v>141</v>
       </c>
       <c r="B2" t="n">
-        <v>920</v>
+        <v>860</v>
       </c>
       <c r="C2" t="n">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -504,7 +504,7 @@
         <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -520,19 +520,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B3" t="n">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="C3" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
@@ -541,10 +541,10 @@
         <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -560,31 +560,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B4" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="C4" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
       <c r="E4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
       <c r="G4" t="n">
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
@@ -600,28 +600,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" t="n">
-        <v>940</v>
+        <v>820</v>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="n">
-        <v>30</v>
-      </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>30</v>
